--- a/artfynd/A 34213-2025 artfynd.xlsx
+++ b/artfynd/A 34213-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>93037773</v>
       </c>
       <c r="B3" t="n">
-        <v>97952</v>
+        <v>97955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34213-2025 artfynd.xlsx
+++ b/artfynd/A 34213-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>93037773</v>
       </c>
       <c r="B3" t="n">
-        <v>97955</v>
+        <v>97963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34213-2025 artfynd.xlsx
+++ b/artfynd/A 34213-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>93037773</v>
       </c>
       <c r="B3" t="n">
-        <v>97963</v>
+        <v>97973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34213-2025 artfynd.xlsx
+++ b/artfynd/A 34213-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>93037773</v>
       </c>
       <c r="B3" t="n">
-        <v>97973</v>
+        <v>97975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34213-2025 artfynd.xlsx
+++ b/artfynd/A 34213-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>93037773</v>
       </c>
       <c r="B3" t="n">
-        <v>97975</v>
+        <v>97976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
